--- a/public/assets/GCP Workshop.xlsx
+++ b/public/assets/GCP Workshop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\amaltas-university-latest\amaltas-university\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782A6781-B6D7-4FA9-9FCF-84707AA035C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB75C5BE-BF61-4F71-AE00-55B6F88F8744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
   <si>
     <t>Full Name</t>
   </si>
@@ -250,12 +250,6 @@
     <t>divakarmishra141@gmail.com</t>
   </si>
   <si>
-    <t>Dr. Harshit Mankad</t>
-  </si>
-  <si>
-    <t>acrajeharsh9425@gmail.com</t>
-  </si>
-  <si>
     <t>Dr. Nomita Mishra</t>
   </si>
   <si>
@@ -356,13 +350,37 @@
   </si>
   <si>
     <t>vijaychlcbcc@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Harshit Mankar</t>
+  </si>
+  <si>
+    <t>Acradeharsh24@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Vinay Patidar</t>
+  </si>
+  <si>
+    <t>dr.vinaypatidar@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr.Farooq khan</t>
+  </si>
+  <si>
+    <t>farooqkhanfrk914@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Abhay Gupta</t>
+  </si>
+  <si>
+    <t>abhay@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -370,13 +388,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -388,13 +420,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -732,15 +768,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C59"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -748,7 +784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -756,7 +792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -764,7 +800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -772,7 +808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -780,15 +816,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -796,7 +833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -804,7 +841,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -812,7 +849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -820,7 +857,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -828,7 +865,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -836,7 +873,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -844,7 +881,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -852,7 +889,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -860,7 +897,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -868,7 +905,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -876,7 +913,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -884,7 +921,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -892,7 +929,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -900,7 +937,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -908,7 +945,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -916,7 +953,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -924,7 +961,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -932,7 +969,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -940,7 +977,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -948,7 +985,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -956,7 +993,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -964,7 +1001,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -972,7 +1009,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -980,7 +1017,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -988,7 +1025,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -996,7 +1033,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -1004,7 +1041,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -1012,7 +1049,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -1020,7 +1057,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1028,7 +1065,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -1036,7 +1073,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -1044,154 +1081,183 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>76</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>78</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>80</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>82</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>84</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>86</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>88</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>90</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>92</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>94</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>96</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>98</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>100</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>102</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>104</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B54" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>106</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>108</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B56" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>110</v>
-      </c>
-      <c r="B56" t="s">
-        <v>111</v>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B39" r:id="rId1" xr:uid="{4B3EB0ED-621A-4717-9495-3DE884A4E11B}"/>
+    <hyperlink ref="B59" r:id="rId2" xr:uid="{5643CE4F-84DC-45E3-B882-EF0E0AE08632}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B56" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B38 A40:B56" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/assets/GCP Workshop.xlsx
+++ b/public/assets/GCP Workshop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\amaltas-university-latest\amaltas-university\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB75C5BE-BF61-4F71-AE00-55B6F88F8744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D14524-826D-4CC1-96EF-78F938C54D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="141">
   <si>
     <t>Full Name</t>
   </si>
@@ -28,12 +28,18 @@
     <t>Email Address</t>
   </si>
   <si>
+    <t>__EMPTY</t>
+  </si>
+  <si>
     <t>Dr. Shahana Shah</t>
   </si>
   <si>
     <t>shahanashah2@gmail.com</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Dr. Palak Chouksey</t>
   </si>
   <si>
@@ -250,6 +256,12 @@
     <t>divakarmishra141@gmail.com</t>
   </si>
   <si>
+    <t>Dr. Harshit Mankar</t>
+  </si>
+  <si>
+    <t>Acradeharsh24@gmail.com</t>
+  </si>
+  <si>
     <t>Dr. Nomita Mishra</t>
   </si>
   <si>
@@ -352,12 +364,6 @@
     <t>vijaychlcbcc@gmail.com</t>
   </si>
   <si>
-    <t>Dr. Harshit Mankar</t>
-  </si>
-  <si>
-    <t>Acradeharsh24@gmail.com</t>
-  </si>
-  <si>
     <t>Dr. Vinay Patidar</t>
   </si>
   <si>
@@ -374,13 +380,76 @@
   </si>
   <si>
     <t>abhay@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Shilpa Bais</t>
+  </si>
+  <si>
+    <t>shilpabais20@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Sunil Chandel</t>
+  </si>
+  <si>
+    <t>schandel272@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Shehla Jaffri</t>
+  </si>
+  <si>
+    <t>tinu.shehla@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Preeti Rai</t>
+  </si>
+  <si>
+    <t>preetirai.ujn@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Ananya Jaiswal</t>
+  </si>
+  <si>
+    <t>anjais.jaiswal921@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Geeta Vishnariya</t>
+  </si>
+  <si>
+    <t>geetavishnariya@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Neha Jain</t>
+  </si>
+  <si>
+    <t>neha18ani@gmail.com</t>
+  </si>
+  <si>
+    <t>dr.rajesmangroliya@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Praveen Narayan Mishra</t>
+  </si>
+  <si>
+    <t>praveennarayanmishra@gmail.com</t>
+  </si>
+  <si>
+    <t>Dr. Abhilasha Dutta</t>
+  </si>
+  <si>
+    <t>abhilasha@gmail.com</t>
+  </si>
+  <si>
+    <t>puneet1984@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Puneet Maheshwari </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -388,27 +457,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -420,17 +475,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -768,12 +819,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.125" customWidth="1"/>
+    <col min="1" max="1" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -783,481 +833,770 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>69</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="B39" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>81</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>83</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>85</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>87</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>89</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>91</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>93</v>
+      </c>
+      <c r="C46" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>95</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B58" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>116</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="B59" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" t="s">
+        <v>125</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" t="s">
+        <v>133</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>10</v>
+      </c>
+      <c r="B67" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>135</v>
+      </c>
+      <c r="B68" t="s">
+        <v>136</v>
+      </c>
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>137</v>
+      </c>
+      <c r="B69" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B39" r:id="rId1" xr:uid="{4B3EB0ED-621A-4717-9495-3DE884A4E11B}"/>
-    <hyperlink ref="B59" r:id="rId2" xr:uid="{5643CE4F-84DC-45E3-B882-EF0E0AE08632}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B38 A40:B56" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C69" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/assets/GCP Workshop.xlsx
+++ b/public/assets/GCP Workshop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\amaltas-university-latest\amaltas-university\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D14524-826D-4CC1-96EF-78F938C54D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6F38B8-B8BA-47C9-90CE-AF09E4473D09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="143">
   <si>
     <t>Full Name</t>
   </si>
@@ -443,6 +443,12 @@
   </si>
   <si>
     <t xml:space="preserve">Dr. Puneet Maheshwari </t>
+  </si>
+  <si>
+    <t>Dr Aman Pratap Singh</t>
+  </si>
+  <si>
+    <t>Amnps23@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -819,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5" bestFit="1" customWidth="1"/>
@@ -1593,6 +1599,14 @@
         <v>139</v>
       </c>
     </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" t="s">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
